--- a/data_mahasiswa_baru.xlsx
+++ b/data_mahasiswa_baru.xlsx
@@ -472,17 +472,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2201001</t>
+          <t>2504001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vero Farida</t>
+          <t>Ratna Kusmawati</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>37949</v>
+        <v>38678</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -505,83 +505,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2202001</t>
+          <t>2403001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jaeman Pradipta</t>
+          <t>Cinthia Agustina</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>37535</v>
+        <v>38535</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2301001</t>
+          <t>2502001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ir. Nadine Thamrin, M.Pd</t>
+          <t>Vega Samosir</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>38097</v>
+        <v>39031</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2501001</t>
+          <t>2504002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mursita Halimah</t>
+          <t>Asirwanda Zulkarnain</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -593,7 +593,7 @@
         <v>2025</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>39167</v>
+        <v>38730</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -604,12 +604,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2201002</t>
+          <t>2201001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Makara Permata</t>
+          <t>Edward Sihombing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -619,14 +619,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>2022</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38125</v>
+        <v>37386</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -637,17 +637,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2103001</t>
+          <t>2102001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Paulin Yulianti</t>
+          <t>Cahyono Kuswoyo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -659,28 +659,28 @@
         <v>2021</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>37683</v>
+        <v>37710</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2202002</t>
+          <t>2303001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Faizah Aryani</t>
+          <t>Sari Kuswandari</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38006</v>
+        <v>38128</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alambana Mayasari</t>
+          <t>Sari Safitri</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -725,7 +725,7 @@
         <v>2024</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>38685</v>
+        <v>38189</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,17 +736,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2204001</t>
+          <t>2301001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Garda Pranowo, M.TI.</t>
+          <t>Citra Melani</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -755,26 +755,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>37321</v>
+        <v>37645</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2204002</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Najwa Rahayu</t>
+          <t>Ani Yuniar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -784,35 +784,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>2022</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>38083</v>
+        <v>37318</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2504001</t>
+          <t>2201002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Heru Marpaung</t>
+          <t>Bakiono Simbolon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>38737</v>
+        <v>37947</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2104001</t>
+          <t>2202001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Artawan Aryani, S.Pt</t>
+          <t>Hesti Farida</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -854,31 +854,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>37401</v>
+        <v>38206</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2402001</t>
+          <t>2501001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paris Maryati</t>
+          <t>Umi Wastuti</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>38147</v>
+        <v>38499</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -901,50 +901,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2501002</t>
+          <t>2102002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cemani Hakim</t>
+          <t>Ajimin Kuswoyo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>38436</v>
+        <v>37414</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2301002</t>
+          <t>2203001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jagaraga Sinaga, S.Ked</t>
+          <t>Vicky Pratiwi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>38217</v>
+        <v>37481</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -967,29 +967,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2204003</t>
+          <t>2303002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suci Anggriawan</t>
+          <t>Wadi Hakim</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>38283</v>
+        <v>37661</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1000,17 +1000,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2501003</t>
+          <t>2304001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hadi Waskita</t>
+          <t>Marwata Saptono</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>39233</v>
+        <v>37981</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1033,17 +1033,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2102001</t>
+          <t>2401002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mumpuni Siregar</t>
+          <t>Rini Laksmiwati</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1052,31 +1052,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>37225</v>
+        <v>39051</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2202003</t>
+          <t>2304002</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bahuraksa Hariyah, M.Kom.</t>
+          <t>Jais Siregar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>37770</v>
+        <v>38113</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1099,17 +1099,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2304001</t>
+          <t>2402001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zulaikha Laksita</t>
+          <t>Ratna Sudiati</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>38694</v>
+        <v>39031</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1132,12 +1132,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2501004</t>
+          <t>2201003</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sutan Argono Prakasa, S.E.I</t>
+          <t>Puti Purwanti</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1147,30 +1147,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>39320</v>
+        <v>38224</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2304002</t>
+          <t>2404001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ayu Kusumo</t>
+          <t>Natalia Puspasari</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>38530</v>
+        <v>38613</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1198,45 +1198,45 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2402002</t>
+          <t>2504003</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Eva Samosir</t>
+          <t>Jefri Budiyanto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>38381</v>
+        <v>38372</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2504002</t>
+          <t>2304003</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kawaca Padmasari</t>
+          <t>Bagya Sitorus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>38892</v>
+        <v>38453</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1264,50 +1264,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2102002</t>
+          <t>2504004</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tasdik Hastuti</t>
+          <t>Belinda Melani</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>37539</v>
+        <v>39010</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2203001</t>
+          <t>2201004</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gilda Permata</t>
+          <t>Ellis Aryani</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1319,40 +1319,40 @@
         <v>2022</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>38237</v>
+        <v>37451</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2103002</t>
+          <t>2504005</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cager Gunawan, S.Farm</t>
+          <t>Eka Novitasari</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>37525</v>
+        <v>38486</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1363,12 +1363,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2501005</t>
+          <t>2301002</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sadina Kusumo, S.T.</t>
+          <t>Uchita Yolanda</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1382,31 +1382,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>38488</v>
+        <v>38414</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2502001</t>
+          <t>2404002</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Unjani Mangunsong, S.Sos</t>
+          <t>Yahya Tampubolon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>39427</v>
+        <v>38852</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1429,17 +1429,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2502002</t>
+          <t>2103001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Malika Mardhiyah, S.I.Kom</t>
+          <t>Keisha Safitri</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>38871</v>
+        <v>37563</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1462,17 +1462,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2402003</t>
+          <t>2203002</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ir. Karma Pudjiastuti, S.Kom</t>
+          <t>Dadap Haryanto</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>38262</v>
+        <v>38337</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1495,12 +1495,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2501006</t>
+          <t>2101001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bagiya Saefullah</t>
+          <t>Karman Latupono</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>39418</v>
+        <v>37173</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1528,17 +1528,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2201003</t>
+          <t>2403002</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Padma Habibi, M.Kom.</t>
+          <t>Mahdi Maryadi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>37344</v>
+        <v>38296</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1561,29 +1561,29 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2103003</t>
+          <t>2404003</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H. Lamar Rahayu</t>
+          <t>Adikara Prasasta</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>37899</v>
+        <v>38635</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1594,12 +1594,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2402004</t>
+          <t>2102003</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R. Dinda Rajata, S.E.</t>
+          <t>Diah Usada</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1613,43 +1613,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>38207</v>
+        <v>37559</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2303001</t>
+          <t>2501002</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ir. Lintang Putra</t>
+          <t>Kunthara Marpaung</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>38531</v>
+        <v>39388</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1660,17 +1660,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2401002</t>
+          <t>2303003</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tgk. Irma Wibisono, M.Farm</t>
+          <t>Soleh Mustofa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>38611</v>
+        <v>38233</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1693,17 +1693,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2201004</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Zahra Megantara</t>
+          <t>Luhung Maheswara</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1715,40 +1715,40 @@
         <v>2022</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>37321</v>
+        <v>37691</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2202004</t>
+          <t>2204003</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dr. Icha Manullang, S.Ked</t>
+          <t>Cawisono Ramadan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>2022</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>38071</v>
+        <v>37803</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1759,12 +1759,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2501007</t>
+          <t>2301003</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Irma Puspita</t>
+          <t>Dwi Zulkarnain</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1774,14 +1774,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>38778</v>
+        <v>38500</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1792,12 +1792,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2202005</t>
+          <t>2202002</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ir. Purwa Hastuti</t>
+          <t>Panca Salahudin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1807,14 +1807,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>2022</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>38284</v>
+        <v>37430</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1825,29 +1825,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2202006</t>
+          <t>2304004</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Drs. Hardi Melani, M.M.</t>
+          <t>Gabriella Usada</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>37803</v>
+        <v>38620</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1858,17 +1858,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2301003</t>
+          <t>2404004</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R.A. Diana Widodo, M.Farm</t>
+          <t>Gantar Nashiruddin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>38475</v>
+        <v>38981</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dimas Nababan</t>
+          <t>Jasmin Usamah</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1913,7 +1913,7 @@
         <v>2022</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>37820</v>
+        <v>37857</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1924,17 +1924,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2301004</t>
+          <t>2204005</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Endah Sihombing</t>
+          <t>Zaenab Rahmawati</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1943,31 +1943,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>37845</v>
+        <v>38141</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2102003</t>
+          <t>2204006</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Prabowo Farida</t>
+          <t>Gaduh Marpaung</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1976,31 +1976,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>37121</v>
+        <v>38006</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2204005</t>
+          <t>2301004</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kasiyah Nashiruddin</t>
+          <t>Amelia Usamah</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>38240</v>
+        <v>37980</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2023,12 +2023,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2203002</t>
+          <t>2203003</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gaman Simbolon, S.E.</t>
+          <t>Kemba Gunawan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2038,14 +2038,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>2022</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>37470</v>
+        <v>38257</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2056,29 +2056,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2203003</t>
+          <t>2501003</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cakrawala Purwanti, M.Ak</t>
+          <t>Maida Nasyiah</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>38331</v>
+        <v>38531</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2089,17 +2089,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2204006</t>
+          <t>2303004</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>T. Marwata Nababan</t>
+          <t>Karsana Dongoran</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>37952</v>
+        <v>38189</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2122,12 +2122,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2104002</t>
+          <t>2304005</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mila Najmudin, M.Pd</t>
+          <t>Kartika Nasyidah</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2137,35 +2137,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>37842</v>
+        <v>37785</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2301005</t>
+          <t>2204007</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H. Karna Safitri</t>
+          <t>Laksana Firmansyah</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2174,43 +2174,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>37932</v>
+        <v>37677</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2501008</t>
+          <t>2503001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bella Yuliarti, M.Pd</t>
+          <t>Darijan Budiman</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>2025</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>39372</v>
+        <v>39124</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2221,17 +2221,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2504003</t>
+          <t>2201005</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kairav Agustina</t>
+          <t>Rika Pratiwi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2240,43 +2240,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>38484</v>
+        <v>38159</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2301006</t>
+          <t>2102004</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ifa Narpati, M.TI.</t>
+          <t>Widya Novitasari</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>37786</v>
+        <v>37114</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2287,12 +2287,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2403001</t>
+          <t>2303005</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Anastasia Oktaviani</t>
+          <t>Nugraha Maheswara</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>38425</v>
+        <v>38223</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2320,17 +2320,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2501009</t>
+          <t>2303006</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Yance Aryani</t>
+          <t>Rudi Waskita</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>38582</v>
+        <v>37827</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2353,78 +2353,78 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2301007</t>
+          <t>2202003</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Amalia Puspasari</t>
+          <t>Zizi Pertiwi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>38464</v>
+        <v>37747</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2203004</t>
+          <t>2401003</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Najwa Aryani, S.T.</t>
+          <t>Bakiman Setiawan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>37973</v>
+        <v>38338</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2502003</t>
+          <t>2502002</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Carub Kuswoyo, S.E.</t>
+          <t>Putu Wahyudin</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2441,7 +2441,7 @@
         <v>2025</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>39217</v>
+        <v>38497</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2452,17 +2452,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2503001</t>
+          <t>2502003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dr. Ratna Rajasa, M.TI.</t>
+          <t>Kunthara Tampubolon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2474,7 +2474,7 @@
         <v>2025</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>39068</v>
+        <v>38585</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2485,29 +2485,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2102004</t>
+          <t>2401004</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agus Laksita</t>
+          <t>Cinthia Yuliarti</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>37336</v>
+        <v>38782</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2518,17 +2518,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2401003</t>
+          <t>2104001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R. Mila Prasasta</t>
+          <t>Paulin Hasanah</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>39013</v>
+        <v>37606</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2551,17 +2551,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2102005</t>
+          <t>2201006</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Drs. Lidya Agustina</t>
+          <t>Cengkir Waluyo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2570,43 +2570,43 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>37793</v>
+        <v>37705</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2201005</t>
+          <t>2202004</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shakila Nasyidah</t>
+          <t>Estiawan Utama</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E66" t="n">
         <v>2022</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>37794</v>
+        <v>37520</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2617,12 +2617,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2303002</t>
+          <t>2203004</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Yance Purwanti</t>
+          <t>Kacung Siregar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>38675</v>
+        <v>38245</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2650,17 +2650,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2404001</t>
+          <t>2203005</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bagas Kuswoyo</t>
+          <t>Balapati Jailani</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>38535</v>
+        <v>37783</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2683,29 +2683,29 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2502004</t>
+          <t>2404005</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sidiq Tarihoran, S.H.</t>
+          <t>Vino Irawan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>38940</v>
+        <v>38514</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2716,12 +2716,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2301008</t>
+          <t>2301005</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vicky Irawan</t>
+          <t>Harsana Najmudin</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2738,7 +2738,7 @@
         <v>2023</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>38312</v>
+        <v>38532</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2749,12 +2749,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2403002</t>
+          <t>2103002</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Karimah Kurniawan</t>
+          <t>Bakda Wijaya</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2764,14 +2764,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>38377</v>
+        <v>37266</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2782,29 +2782,29 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2204007</t>
+          <t>2402002</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lurhur Mayasari</t>
+          <t>Hardana Samosir</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>37308</v>
+        <v>38728</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2815,17 +2815,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2203005</t>
+          <t>2104002</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Unggul Rahayu</t>
+          <t>Sidiq Haryanto</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>37735</v>
+        <v>37690</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2848,12 +2848,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2504004</t>
+          <t>2204008</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tgk. Kusuma Kusmawati</t>
+          <t>Dasa Pangestu</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>38626</v>
+        <v>37818</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2881,17 +2881,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2103004</t>
+          <t>2304006</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dr. Tari Pratiwi</t>
+          <t>Bagas Mandala</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2900,31 +2900,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>37326</v>
+        <v>38287</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2304003</t>
+          <t>2401005</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Juli Haryanto</t>
+          <t>Gara Wibowo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>37745</v>
+        <v>38406</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2947,17 +2947,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2203006</t>
+          <t>2401006</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Opan Budiyanto</t>
+          <t>Kezia Puspasari</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>37443</v>
+        <v>38466</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2980,12 +2980,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2301009</t>
+          <t>2401007</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vega Wastuti, S.T.</t>
+          <t>Cengkal Pradana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2995,14 +2995,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>38195</v>
+        <v>38965</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3013,17 +3013,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2502005</t>
+          <t>2404006</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nyoman Suwarno</t>
+          <t>Samiah Kuswandari</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>38836</v>
+        <v>38913</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3046,17 +3046,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2504005</t>
+          <t>2301006</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Luluh Riyanti</t>
+          <t>Vega Lazuardi</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3065,10 +3065,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>38417</v>
+        <v>38415</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3079,17 +3079,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2203007</t>
+          <t>2102005</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Zamira Melani</t>
+          <t>Eka Winarsih</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>38347</v>
+        <v>37003</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3112,17 +3112,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2301010</t>
+          <t>2404007</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Paiman Uwais</t>
+          <t>Aisyah Riyanti</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>37965</v>
+        <v>38273</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3145,29 +3145,29 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2501010</t>
+          <t>2203006</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Olivia Budiyanto, S.Psi</t>
+          <t>Yulia Namaga</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>39027</v>
+        <v>37898</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3178,12 +3178,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2204008</t>
+          <t>2404008</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kamila Lailasari</t>
+          <t>Balapati Jailani</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3193,14 +3193,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>37939</v>
+        <v>38940</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3211,17 +3211,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2102006</t>
+          <t>2101002</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hafshah Mustofa</t>
+          <t>Indah Kuswandari</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3233,7 +3233,7 @@
         <v>2021</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>37360</v>
+        <v>36963</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3244,17 +3244,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2504006</t>
+          <t>2102006</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tugiman Suryatmi</t>
+          <t>Dono Saputra</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>39259</v>
+        <v>37582</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3277,12 +3277,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2204009</t>
+          <t>2404009</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Catur Megantara</t>
+          <t>Ina Hartati</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>37835</v>
+        <v>38057</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3310,62 +3310,62 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2403003</t>
+          <t>2402003</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cecep Wibisono</t>
+          <t>Martana Megantara</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>2024</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>38740</v>
+        <v>38627</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2202007</t>
+          <t>2501004</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rina Rahmawati</t>
+          <t>Paiman Siregar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>38344</v>
+        <v>39023</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3376,12 +3376,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2502006</t>
+          <t>2402004</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jelita Pradana</t>
+          <t>Nilam Uyainah</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3391,30 +3391,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>39187</v>
+        <v>38387</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2502007</t>
+          <t>2402005</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>R. Jaga Megantara</t>
+          <t>Satya Gunarto</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3428,31 +3428,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>38401</v>
+        <v>38923</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2304004</t>
+          <t>2401008</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Balamantri Kuswoyo</t>
+          <t>Kenzie Firgantoro</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>37780</v>
+        <v>38632</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3475,17 +3475,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2303003</t>
+          <t>2502004</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>R.M. Galang Tarihoran, S.Psi</t>
+          <t>Iriana Widiastuti</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>38027</v>
+        <v>39175</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3508,12 +3508,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2202008</t>
+          <t>2402006</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kasiyah Prastuti</t>
+          <t>Ellis Pertiwi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3527,64 +3527,64 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>38015</v>
+        <v>38091</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2301011</t>
+          <t>2502005</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Betania Palastri, M.TI.</t>
+          <t>Faizah Suryatmi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>38711</v>
+        <v>38746</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2303004</t>
+          <t>2301007</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Puji Yuliarti</t>
+          <t>Gara Mangunsong</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3596,7 +3596,7 @@
         <v>2023</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>38447</v>
+        <v>38508</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3607,45 +3607,45 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2203008</t>
+          <t>2102007</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Karya Hariyah</t>
+          <t>Murti Wasita</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>38215</v>
+        <v>37181</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2103005</t>
+          <t>2103003</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Luthfi Zulaika</t>
+          <t>Raina Yuliarti</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3655,35 +3655,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>2021</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>37653</v>
+        <v>37668</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2401004</t>
+          <t>2404010</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Luwes Hutapea, S.Sos</t>
+          <t>Lega Wibisono</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3695,23 +3695,23 @@
         <v>2024</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>38962</v>
+        <v>38286</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2204010</t>
+          <t>2204009</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>drg. Mutia Maryadi, M.Pd</t>
+          <t>Mumpuni Samosir</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3721,14 +3721,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>2022</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>37507</v>
+        <v>38175</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3739,17 +3739,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2104003</t>
+          <t>2402007</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Zulfa Natsir</t>
+          <t>Samiah Wijayanti</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3758,14 +3758,14 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>37149</v>
+        <v>38755</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>

--- a/data_mahasiswa_baru.xlsx
+++ b/data_mahasiswa_baru.xlsx
@@ -472,17 +472,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2504001</t>
+          <t>2103001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ratna Kusmawati</t>
+          <t>Tantri Sudiati</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,26 +491,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>38678</v>
+        <v>37177</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2403001</t>
+          <t>2203001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cinthia Agustina</t>
+          <t>Galak Pangestu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,14 +520,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>38535</v>
+        <v>38193</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2502001</t>
+          <t>2403001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vega Samosir</t>
+          <t>Galar Thamrin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>39031</v>
+        <v>38474</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -571,17 +571,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2504002</t>
+          <t>2403002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Asirwanda Zulkarnain</t>
+          <t>Atma Adriansyah</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,31 +590,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38730</v>
+        <v>38577</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2201001</t>
+          <t>2403003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Edward Sihombing</t>
+          <t>Pranata Firmansyah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>37386</v>
+        <v>38582</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -637,12 +637,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2102001</t>
+          <t>2302001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cahyono Kuswoyo</t>
+          <t>Daliono Utama</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>37710</v>
+        <v>38317</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -670,17 +670,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2303001</t>
+          <t>2304001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sari Kuswandari</t>
+          <t>Carla Uyainah</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -692,7 +692,7 @@
         <v>2023</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38128</v>
+        <v>37946</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -703,29 +703,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2401001</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sari Safitri</t>
+          <t>Cecep Halim</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>38189</v>
+        <v>37668</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,29 +736,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2301001</t>
+          <t>2102001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Citra Melani</t>
+          <t>Tasdik Putra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>37645</v>
+        <v>37070</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -769,17 +769,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2204001</t>
+          <t>2103002</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ani Yuniar</t>
+          <t>Hafshah Susanti</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -788,76 +788,76 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>37318</v>
+        <v>37490</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2201002</t>
+          <t>2404001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bakiono Simbolon</t>
+          <t>Farah Padmasari</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>37947</v>
+        <v>38929</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2202001</t>
+          <t>2201001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hesti Farida</t>
+          <t>Adikara Anggriawan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>2022</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>38206</v>
+        <v>38257</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -868,17 +868,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2501001</t>
+          <t>2304002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Umi Wastuti</t>
+          <t>Putri Permata</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>38499</v>
+        <v>38689</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -901,17 +901,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2102002</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajimin Kuswoyo</t>
+          <t>Mumpuni Nashiruddin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>37414</v>
+        <v>37766</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -934,29 +934,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2203001</t>
+          <t>2402001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vicky Pratiwi</t>
+          <t>Agus Nainggolan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>37481</v>
+        <v>38661</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -967,17 +967,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2303002</t>
+          <t>2302002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wadi Hakim</t>
+          <t>Lamar Prasasta</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -989,28 +989,28 @@
         <v>2023</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>37661</v>
+        <v>38619</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2304001</t>
+          <t>2303001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Marwata Saptono</t>
+          <t>Nasrullah Pradipta</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1022,7 +1022,7 @@
         <v>2023</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>37981</v>
+        <v>38584</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1033,17 +1033,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2401002</t>
+          <t>2202001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rini Laksmiwati</t>
+          <t>Paramita Kuswandari</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1052,31 +1052,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>39051</v>
+        <v>37331</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2304002</t>
+          <t>2403004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jais Siregar</t>
+          <t>Warsa Sitorus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>38113</v>
+        <v>38713</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1099,12 +1099,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2402001</t>
+          <t>2402002</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ratna Sudiati</t>
+          <t>Prakosa Haryanto</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1114,14 +1114,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>2024</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>39031</v>
+        <v>38128</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1132,17 +1132,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2201003</t>
+          <t>2304003</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Puti Purwanti</t>
+          <t>Yuni Usada</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1151,31 +1151,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>38224</v>
+        <v>38167</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2404001</t>
+          <t>2103003</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Natalia Puspasari</t>
+          <t>Anita Suryatmi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>38613</v>
+        <v>37366</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1198,50 +1198,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2504003</t>
+          <t>2403005</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jefri Budiyanto</t>
+          <t>Ifa Hassanah</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>38372</v>
+        <v>38310</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2304003</t>
+          <t>2303002</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bagya Sitorus</t>
+          <t>Kardi Uwais</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1253,7 +1253,7 @@
         <v>2023</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>38453</v>
+        <v>38309</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1264,17 +1264,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2504004</t>
+          <t>2202002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Belinda Melani</t>
+          <t>Maya Mardhiyah</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1283,26 +1283,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>39010</v>
+        <v>38167</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2201004</t>
+          <t>2201002</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ellis Aryani</t>
+          <t>Lega Winarno</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1312,14 +1312,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>2022</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>37451</v>
+        <v>37975</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1330,17 +1330,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2504005</t>
+          <t>2201003</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eka Novitasari</t>
+          <t>Juli Purnawati</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>38486</v>
+        <v>37486</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1363,45 +1363,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2301002</t>
+          <t>2404002</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Uchita Yolanda</t>
+          <t>Vinsen Marbun</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>38414</v>
+        <v>38657</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2404002</t>
+          <t>2304004</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yahya Tampubolon</t>
+          <t>Melinda Mandasari</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1411,14 +1411,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>38852</v>
+        <v>38524</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1429,29 +1429,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2103001</t>
+          <t>2404003</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Keisha Safitri</t>
+          <t>Gamani Saptono</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>37563</v>
+        <v>38258</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1462,17 +1462,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2203002</t>
+          <t>2201004</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dadap Haryanto</t>
+          <t>Wisnu Zulkarnain</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1484,7 +1484,7 @@
         <v>2022</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>38337</v>
+        <v>37418</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1495,17 +1495,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2101001</t>
+          <t>2203002</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Karman Latupono</t>
+          <t>Karna Saptono</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>37173</v>
+        <v>37436</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1528,62 +1528,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2403002</t>
+          <t>2304005</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mahdi Maryadi</t>
+          <t>Sakura Laksita</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>38296</v>
+        <v>38010</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2404003</t>
+          <t>2303003</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Adikara Prasasta</t>
+          <t>Lili Puspasari</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>38635</v>
+        <v>37691</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1594,17 +1594,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2102003</t>
+          <t>2304006</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diah Usada</t>
+          <t>Lintang Laksita</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>37559</v>
+        <v>37907</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1627,29 +1627,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2501002</t>
+          <t>2303004</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kunthara Marpaung</t>
+          <t>Farhunnisa Pudjiastuti</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>39388</v>
+        <v>37721</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1660,12 +1660,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2303003</t>
+          <t>2503001</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Soleh Mustofa</t>
+          <t>Intan Wahyuni</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1675,14 +1675,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>38233</v>
+        <v>38627</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1693,12 +1693,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2204002</t>
+          <t>2504001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Luhung Maheswara</t>
+          <t>Bagus Simanjuntak</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1712,43 +1712,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>37691</v>
+        <v>39282</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2204003</t>
+          <t>2102002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cawisono Ramadan</t>
+          <t>Pia Purnawati</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>37803</v>
+        <v>37258</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1759,29 +1759,29 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2301003</t>
+          <t>2504002</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dwi Zulkarnain</t>
+          <t>Kasiyah Nasyidah</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>38500</v>
+        <v>38955</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1792,29 +1792,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2202002</t>
+          <t>2404004</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Panca Salahudin</t>
+          <t>Febi Melani</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>37430</v>
+        <v>38209</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1825,45 +1825,45 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2304004</t>
+          <t>2101001</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gabriella Usada</t>
+          <t>Lantar Nainggolan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>38620</v>
+        <v>36941</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2404004</t>
+          <t>2304007</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gantar Nashiruddin</t>
+          <t>Ajimin Hutapea</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>38981</v>
+        <v>38378</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1891,29 +1891,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2204004</t>
+          <t>2401001</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jasmin Usamah</t>
+          <t>Harjasa Budiman</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>37857</v>
+        <v>38956</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1924,12 +1924,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2204005</t>
+          <t>2104001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zaenab Rahmawati</t>
+          <t>Reksa Sihombing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1939,47 +1939,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>38141</v>
+        <v>37038</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2204006</t>
+          <t>2401002</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gaduh Marpaung</t>
+          <t>Sakura Yuniar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>38006</v>
+        <v>38416</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1990,29 +1990,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2301004</t>
+          <t>2102003</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amelia Usamah</t>
+          <t>Jaka Kuswoyo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>37980</v>
+        <v>36922</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2023,12 +2023,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2203003</t>
+          <t>2103004</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kemba Gunawan</t>
+          <t>Elma Utami</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2038,14 +2038,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>38257</v>
+        <v>37886</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2056,29 +2056,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2501003</t>
+          <t>2204003</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Maida Nasyiah</t>
+          <t>Utama Nashiruddin</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>38531</v>
+        <v>37899</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2089,29 +2089,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2303004</t>
+          <t>2504003</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Karsana Dongoran</t>
+          <t>Kasiyah Anggraini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>38189</v>
+        <v>39292</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2122,29 +2122,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2304005</t>
+          <t>2102004</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kartika Nasyidah</t>
+          <t>Rendy Budiman</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>37785</v>
+        <v>37979</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2155,17 +2155,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2204007</t>
+          <t>2303005</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Laksana Firmansyah</t>
+          <t>Setya Hardiansyah</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>37677</v>
+        <v>38154</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2188,29 +2188,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2503001</t>
+          <t>2401003</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Darijan Budiman</t>
+          <t>Aurora Yolanda</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>39124</v>
+        <v>38945</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2221,17 +2221,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2201005</t>
+          <t>2104002</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rika Pratiwi</t>
+          <t>Usyi Andriani</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2240,43 +2240,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>38159</v>
+        <v>37418</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2102004</t>
+          <t>2404005</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Widya Novitasari</t>
+          <t>Slamet Nugroho</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>37114</v>
+        <v>39017</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2287,17 +2287,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2303005</t>
+          <t>2404006</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nugraha Maheswara</t>
+          <t>Nardi Hidayat</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>38223</v>
+        <v>38250</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2320,17 +2320,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2303006</t>
+          <t>2302003</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rudi Waskita</t>
+          <t>Sabri Anggriawan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2342,7 +2342,7 @@
         <v>2023</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>37827</v>
+        <v>37627</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2353,17 +2353,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2202003</t>
+          <t>2103005</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zizi Pertiwi</t>
+          <t>Yulia Permata</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>37747</v>
+        <v>37953</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2386,45 +2386,45 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2401003</t>
+          <t>2304008</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bakiman Setiawan</t>
+          <t>Siti Usamah</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>38338</v>
+        <v>38434</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2502002</t>
+          <t>2202003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Putu Wahyudin</t>
+          <t>Ulva Rahmawati</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2434,14 +2434,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>38497</v>
+        <v>37626</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2452,50 +2452,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2502003</t>
+          <t>2301001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kunthara Tampubolon</t>
+          <t>Usyi Farida</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>38585</v>
+        <v>38518</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2401004</t>
+          <t>2302004</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cinthia Yuliarti</t>
+          <t>Hasna Laksmiwati</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>38782</v>
+        <v>37891</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2518,29 +2518,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2104001</t>
+          <t>2301002</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Paulin Hasanah</t>
+          <t>Dariati Suryono</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>37606</v>
+        <v>38099</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2551,12 +2551,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2201006</t>
+          <t>2401004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cengkir Waluyo</t>
+          <t>Daru Nugroho</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>37705</v>
+        <v>39057</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2584,17 +2584,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2202004</t>
+          <t>2203003</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Estiawan Utama</t>
+          <t>Teguh Hidayanto</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2606,7 +2606,7 @@
         <v>2022</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>37520</v>
+        <v>37420</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2617,29 +2617,29 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2203004</t>
+          <t>2104003</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kacung Siregar</t>
+          <t>Ellis Handayani</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>38245</v>
+        <v>37791</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2650,12 +2650,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2203005</t>
+          <t>2103006</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Balapati Jailani</t>
+          <t>Elon Prakasa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2669,26 +2669,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>37783</v>
+        <v>37055</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Lulus</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2404005</t>
+          <t>2204004</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vino Irawan</t>
+          <t>Viman Sinaga</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>38514</v>
+        <v>37424</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2716,17 +2716,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2301005</t>
+          <t>2402003</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Harsana Najmudin</t>
+          <t>Daliono Samosir</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>38532</v>
+        <v>39078</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2749,17 +2749,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2103002</t>
+          <t>2504004</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bakda Wijaya</t>
+          <t>Asmianto Damanik</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>37266</v>
+        <v>38928</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2782,17 +2782,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2402002</t>
+          <t>2303006</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hardana Samosir</t>
+          <t>Muni Pradana</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2801,43 +2801,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>38728</v>
+        <v>38658</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2104002</t>
+          <t>2102005</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sidiq Haryanto</t>
+          <t>Mutia Safitri</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>2021</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>37690</v>
+        <v>37925</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2848,29 +2848,29 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2204008</t>
+          <t>2402004</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dasa Pangestu</t>
+          <t>Titin Anggraini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>37818</v>
+        <v>38473</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2881,45 +2881,45 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2304006</t>
+          <t>2402005</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bagas Mandala</t>
+          <t>Oliva Wahyuni</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>38287</v>
+        <v>39025</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2401005</t>
+          <t>2501001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gara Wibowo</t>
+          <t>Cemeti Halim</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>38406</v>
+        <v>38494</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2947,12 +2947,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2401006</t>
+          <t>2501002</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kezia Puspasari</t>
+          <t>Galang Wijaya</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2962,14 +2962,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>38466</v>
+        <v>38658</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2980,12 +2980,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2401007</t>
+          <t>2301003</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cengkal Pradana</t>
+          <t>Prabowo Ramadan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>38965</v>
+        <v>37970</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3013,12 +3013,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2404006</t>
+          <t>2104004</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Samiah Kuswandari</t>
+          <t>Gilang Saptono</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3028,30 +3028,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>38913</v>
+        <v>37961</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2301006</t>
+          <t>2101002</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Vega Lazuardi</t>
+          <t>Ulya Susanti</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3061,14 +3061,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>38415</v>
+        <v>36983</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3079,29 +3079,29 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2102005</t>
+          <t>2104005</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Eka Winarsih</t>
+          <t>Satya Hutagalung</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E81" t="n">
         <v>2021</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>37003</v>
+        <v>37660</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3112,29 +3112,29 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2404007</t>
+          <t>2301004</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Aisyah Riyanti</t>
+          <t>Baktianto Irawan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>38273</v>
+        <v>37790</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3145,29 +3145,29 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2203006</t>
+          <t>2404007</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Yulia Namaga</t>
+          <t>Umay Firmansyah</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>37898</v>
+        <v>38529</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3178,29 +3178,29 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2404008</t>
+          <t>2201005</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Balapati Jailani</t>
+          <t>Rina Wulandari</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>38940</v>
+        <v>38217</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3211,17 +3211,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2101002</t>
+          <t>2304009</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Indah Kuswandari</t>
+          <t>Siska Farida</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>36963</v>
+        <v>38227</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3244,29 +3244,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2102006</t>
+          <t>2501003</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dono Saputra</t>
+          <t>Aisyah Suartini</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>37582</v>
+        <v>39416</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3277,17 +3277,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2404009</t>
+          <t>2202004</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ina Hartati</t>
+          <t>Raina Puspasari</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>38057</v>
+        <v>37899</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3310,29 +3310,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2402003</t>
+          <t>2404008</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Martana Megantara</t>
+          <t>Intan Hassanah</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>2024</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>38627</v>
+        <v>38079</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3343,17 +3343,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2501004</t>
+          <t>2104006</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Paiman Siregar</t>
+          <t>Ibrani Widodo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>39023</v>
+        <v>36956</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3376,62 +3376,62 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2402004</t>
+          <t>2204005</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nilam Uyainah</t>
+          <t>Kuncara Narpati</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>38387</v>
+        <v>37258</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2402005</t>
+          <t>2103007</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Satya Gunarto</t>
+          <t>Cindy Hartati</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>38923</v>
+        <v>37301</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3442,29 +3442,29 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2401008</t>
+          <t>2502001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kenzie Firgantoro</t>
+          <t>Irma Astuti</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>38632</v>
+        <v>39258</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3475,29 +3475,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2502004</t>
+          <t>2503002</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Iriana Widiastuti</t>
+          <t>Lukita Santoso</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>2025</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>39175</v>
+        <v>38985</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3508,17 +3508,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2402006</t>
+          <t>2301005</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ellis Pertiwi</t>
+          <t>Clara Wulandari</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>38091</v>
+        <v>38264</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3541,12 +3541,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2502005</t>
+          <t>2202005</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Faizah Suryatmi</t>
+          <t>Syahrini Novitasari</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>38746</v>
+        <v>37407</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3574,29 +3574,29 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2301007</t>
+          <t>2402006</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Gara Mangunsong</t>
+          <t>Devi Yulianti</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>38508</v>
+        <v>38639</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3607,50 +3607,50 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2102007</t>
+          <t>2203004</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Murti Wasita</t>
+          <t>Jessica Padmasari</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>37181</v>
+        <v>37982</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2103003</t>
+          <t>2102006</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Raina Yuliarti</t>
+          <t>Padma Hariyah</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3662,61 +3662,61 @@
         <v>2021</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>37668</v>
+        <v>37597</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2404010</t>
+          <t>2102007</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lega Wibisono</t>
+          <t>Puspa Susanti</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>38286</v>
+        <v>37195</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2204009</t>
+          <t>2503003</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mumpuni Samosir</t>
+          <t>Karya Hidayanto</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>38175</v>
+        <v>39283</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2402007</t>
+          <t>2302005</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Samiah Wijayanti</t>
+          <t>Dimas Sitorus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3754,18 +3754,18 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>38755</v>
+        <v>37745</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lulus</t>
+          <t>Aktif</t>
         </is>
       </c>
     </row>
